--- a/artfynd/A 24797-2022 artfynd.xlsx
+++ b/artfynd/A 24797-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24797-2022 artfynd.xlsx
+++ b/artfynd/A 24797-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99367925</v>
+        <v>99368488</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>102952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>FM-45-4-78, Upl</t>
+          <t>FM-9450-1-50, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>674294.3436994663</v>
+        <v>674269</v>
       </c>
       <c r="R2" t="n">
-        <v>6698309.77260662</v>
+        <v>6698202</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-05-30</t>
+          <t>2003-05-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>04:38</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-05-30</t>
+          <t>2003-05-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>04:38</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,6 +783,696 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>99368490</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58463</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>FM-9450-1-50, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>674269</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6698202</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2003-05-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>05:53</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2003-05-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>05:53</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>99366532</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>FM-6220-5-49, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>674266</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6698215</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99366580</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>FM-6180-3-88, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>674257</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6698304</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>99366581</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>FM-6180-3-88, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>674257</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6698304</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>99368489</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>FM-9450-1-50, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>674269</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6698202</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2003-05-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>05:53</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2003-05-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>05:53</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>99367925</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>FM-45-4-78, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>674295</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6698310</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2013-05-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>04:38</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2013-05-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>04:38</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Forsmark platsundersökning</t>
         </is>

--- a/artfynd/A 24797-2022 artfynd.xlsx
+++ b/artfynd/A 24797-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99368488</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99368490</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99366532</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99366580</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99366581</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99368489</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,8 +1512,22 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99367925</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>